--- a/stories/arbres/TREE-SAN-018.xlsx
+++ b/stories/arbres/TREE-SAN-018.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo rentre. Papa dit : on se lave les mains. Avant de manger. Après les toilettes. Savon et eau. Kenzo ouvre l'eau. Il frotte le savon. Il rince. Il essuie.</t>
+          <t>Kenzo rentre. On se lave les mains. Avant de manger. Après les toilettes. Savon et eau. Kenzo ouvre l'eau. Il frotte le savon. Il rince. Il essuie.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rentre.
+papa|On se lave les mains. Avant de manger. Après les toilettes. Savon et eau.
+narrateur|Kenzo ouvre l'eau. Il frotte le savon. Il rince. Il essuie.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre avant le repas, après les toilettes, ou après le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1682,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers avant le repas. L'eau est tiède. papa est tout près. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1867,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2040,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Kenzo a retenu. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. On continue avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2235,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le savon, l'eau, ou la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2402,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le savon. Ça mousse. papa montre lentement. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2539,6 +2593,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2701,6 +2760,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. Papa est près. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2927,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3094,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. Un oiseau chante. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3261,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3428,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. La lumière est claire. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3595,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3762,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi l'eau. Les gouttes tombent. papa montre lentement. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3859,6 +3953,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4021,6 +4120,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. Un oiseau chante. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4287,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4454,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. La lumière est claire. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4621,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4788,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. Les mains brillent. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4955,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5122,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la serviette. Le carrelage est frais. papa montre lentement. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5313,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5341,6 +5480,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. La lumière est claire. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5647,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5814,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. Les mains brillent. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5981,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6148,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. Le savon glisse. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6315,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6313,6 +6482,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers après les toilettes. Le savon sent la menthe. papa est tout près. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6495,6 +6669,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se lave les mains. Avec quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6519,7 +6698,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kenzo respire. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit : je suis là.</t>
+          <t>Kenzo respire. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. Je suis là.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6661,6 +6840,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo respire. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes.
+papa|Je suis là.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7036,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le savon, l'eau, ou la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7203,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le savon. Papa est près. papa montre lentement. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7199,6 +7394,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7361,6 +7561,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. Un oiseau chante. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7728,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7895,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. La lumière est claire. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8062,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8229,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. Les mains brillent. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8396,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8563,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi l'eau. Un oiseau chante. papa montre lentement. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8754,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8681,6 +8921,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. La lumière est claire. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9088,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9005,6 +9255,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. Les mains brillent. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9422,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9329,6 +9589,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. Le savon glisse. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9756,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9923,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la serviette. La lumière est claire. papa montre lentement. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9839,6 +10114,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10001,6 +10281,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. Les mains brillent. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10163,6 +10448,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10325,6 +10615,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. Le savon glisse. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10487,6 +10782,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10649,6 +10949,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. L'eau coule. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10811,6 +11116,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10973,6 +11283,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va vers après le jardin. La serviette est douce. papa est tout près. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11468,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo se lave les mains. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11641,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|C'est juste. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. Kenzo donne la main à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11511,6 +11836,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le savon, l'eau, ou la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11673,6 +12003,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi le savon. Les mains brillent. papa montre lentement. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11859,6 +12194,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12021,6 +12361,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. La lumière est claire. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12528,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12345,6 +12695,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. Les mains brillent. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12862,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12669,6 +13029,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. Le savon glisse. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13196,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13363,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi l'eau. Le savon glisse. papa montre lentement. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13179,6 +13554,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13341,6 +13721,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. Les mains brillent. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13503,6 +13888,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13665,6 +14055,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. Le savon glisse. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13827,6 +14222,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13989,6 +14389,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. L'eau coule. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14151,6 +14556,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14313,6 +14723,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a choisi la serviette. L'eau coule. papa montre lentement. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14499,6 +14914,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14661,6 +15081,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la cuisine. Le savon glisse. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14823,6 +15248,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14985,6 +15415,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint la table. L'eau coule. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15147,6 +15582,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15309,6 +15749,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo rejoint le jardin. L'eau est tiède. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis la serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15471,6 +15916,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15489,7 +15939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15506,6 +15956,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-018.xlsx
+++ b/stories/arbres/TREE-SAN-018.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Kenzo ouvre l'eau. Il frotte le savon. Il rince. Il essuie.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre avant le repas, après les toilettes, ou après le jardin.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1687,6 +1694,7 @@
           <t>narrateur|Kenzo va vers avant le repas. L'eau est tiède. papa est tout près. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1874,6 +1882,7 @@
           <t>narrateur|Kenzo se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2045,6 +2054,7 @@
           <t>narrateur|Oui. Kenzo a retenu. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. On continue avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2240,6 +2250,7 @@
           <t>narrateur|On peut prendre le savon, l'eau, ou la serviette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2407,6 +2418,7 @@
           <t>narrateur|Kenzo a choisi le savon. Ça mousse. papa montre lentement. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2598,6 +2610,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2765,6 +2778,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. Papa est près. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis le savon.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2932,6 +2946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3099,6 +3114,7 @@
           <t>narrateur|Kenzo rejoint la table. Un oiseau chante. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis le savon.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3266,6 +3282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3433,6 +3450,7 @@
           <t>narrateur|Kenzo rejoint le jardin. La lumière est claire. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis le savon.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3600,6 +3618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3767,6 +3786,7 @@
           <t>narrateur|Kenzo a choisi l'eau. Les gouttes tombent. papa montre lentement. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3958,6 +3978,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4125,6 +4146,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. Un oiseau chante. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4292,6 +4314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4459,6 +4482,7 @@
           <t>narrateur|Kenzo rejoint la table. La lumière est claire. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4626,6 +4650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4793,6 +4818,7 @@
           <t>narrateur|Kenzo rejoint le jardin. Les mains brillent. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4960,6 +4986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5127,6 +5154,7 @@
           <t>narrateur|Kenzo a choisi la serviette. Le carrelage est frais. papa montre lentement. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5318,6 +5346,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5485,6 +5514,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. La lumière est claire. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5652,6 +5682,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5819,6 +5850,7 @@
           <t>narrateur|Kenzo rejoint la table. Les mains brillent. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5986,6 +6018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6153,6 +6186,7 @@
           <t>narrateur|Kenzo rejoint le jardin. Le savon glisse. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. avant le repas, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6320,6 +6354,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6487,6 +6522,7 @@
           <t>narrateur|Kenzo va vers après les toilettes. Le savon sent la menthe. papa est tout près. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa sourit.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6674,6 +6710,7 @@
           <t>narrateur|Kenzo se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6846,6 +6883,7 @@
 papa|Je suis là.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7041,6 +7079,7 @@
           <t>narrateur|On peut prendre le savon, l'eau, ou la serviette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7208,6 +7247,7 @@
           <t>narrateur|Kenzo a choisi le savon. Papa est près. papa montre lentement. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7399,6 +7439,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7566,6 +7607,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. Un oiseau chante. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis le savon.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7733,6 +7775,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7900,6 +7943,7 @@
           <t>narrateur|Kenzo rejoint la table. La lumière est claire. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis le savon.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8067,6 +8111,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8234,6 +8279,7 @@
           <t>narrateur|Kenzo rejoint le jardin. Les mains brillent. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis le savon.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8401,6 +8447,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8568,6 +8615,7 @@
           <t>narrateur|Kenzo a choisi l'eau. Un oiseau chante. papa montre lentement. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8759,6 +8807,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8926,6 +8975,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. La lumière est claire. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9093,6 +9143,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9260,6 +9311,7 @@
           <t>narrateur|Kenzo rejoint la table. Les mains brillent. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9427,6 +9479,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9594,6 +9647,7 @@
           <t>narrateur|Kenzo rejoint le jardin. Le savon glisse. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9761,6 +9815,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9928,6 +9983,7 @@
           <t>narrateur|Kenzo a choisi la serviette. La lumière est claire. papa montre lentement. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10119,6 +10175,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10286,6 +10343,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. Les mains brillent. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10453,6 +10511,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10620,6 +10679,7 @@
           <t>narrateur|Kenzo rejoint la table. Le savon glisse. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10787,6 +10847,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10954,6 +11015,7 @@
           <t>narrateur|Kenzo rejoint le jardin. L'eau coule. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après les toilettes, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11121,6 +11183,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11288,6 +11351,7 @@
           <t>narrateur|Kenzo va vers après le jardin. La serviette est douce. papa est tout près. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11475,6 +11539,7 @@
           <t>narrateur|Kenzo se lave les mains. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11646,6 +11711,7 @@
           <t>narrateur|C'est juste. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. Kenzo donne la main à papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11841,6 +11907,7 @@
           <t>narrateur|On peut prendre le savon, l'eau, ou la serviette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12008,6 +12075,7 @@
           <t>narrateur|Kenzo a choisi le savon. Les mains brillent. papa montre lentement. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12199,6 +12267,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12366,6 +12435,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. La lumière est claire. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis le savon.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12533,6 +12603,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12700,6 +12771,7 @@
           <t>narrateur|Kenzo rejoint la table. Les mains brillent. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis le savon.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12867,6 +12939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13034,6 +13107,7 @@
           <t>narrateur|Kenzo rejoint le jardin. Le savon glisse. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis le savon.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13201,6 +13275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13368,6 +13443,7 @@
           <t>narrateur|Kenzo a choisi l'eau. Le savon glisse. papa montre lentement. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13559,6 +13635,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13726,6 +13803,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. Les mains brillent. Kenzo ouvre l'eau. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13893,6 +13971,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14060,6 +14139,7 @@
           <t>narrateur|Kenzo rejoint la table. Le savon glisse. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14227,6 +14307,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14394,6 +14475,7 @@
           <t>narrateur|Kenzo rejoint le jardin. L'eau coule. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis l'eau.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14561,6 +14643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14728,6 +14811,7 @@
           <t>narrateur|Kenzo a choisi la serviette. L'eau coule. papa montre lentement. Kenzo prend le savon. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14919,6 +15003,7 @@
           <t>narrateur|On peut prendre la cuisine, la table, ou le jardin.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15086,6 +15171,7 @@
           <t>narrateur|Kenzo rejoint la cuisine. Le savon glisse. Kenzo rince. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15253,6 +15339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15420,6 +15507,7 @@
           <t>narrateur|Kenzo rejoint la table. L'eau coule. Kenzo essuie. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15587,6 +15675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15754,6 +15843,7 @@
           <t>narrateur|Kenzo rejoint le jardin. L'eau est tiède. Kenzo frotte les mains. Kenzo ouvre l'eau. Il prend le savon. Avant de manger. Après les toilettes. papa dit merci. après le jardin, puis la serviette.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15921,6 +16011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15939,7 +16030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15963,6 +16054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15977,7 +16082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16164,6 +16269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
